--- a/model/ADR_decomposition.xlsx
+++ b/model/ADR_decomposition.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="166">
   <si>
     <t>ABNB ADR decomposition</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Scripts</t>
   </si>
   <si>
-    <t>analysis/src/adr/01-09; data in data/processed/adr/</t>
+    <t>analysis/src/adr/01-10; data in data/processed/adr/. 10 is the audit.</t>
   </si>
   <si>
     <t>Rebuild</t>
@@ -78,7 +78,7 @@
     <t>2_Decomposition</t>
   </si>
   <si>
-    <t>Annual four-way split with an explicit UNEXPLAINED line. Price is measured externally rather than used as the plug, so the terms do not sum to zero by construction - the gap is the point.</t>
+    <t>Annual split into geographic mix, FX, interaction and within-region ADR ex-FX, with the last broken down as far as disclosure allows. REVISED 8 Sep after an audit; it now reconciles to the independent 10-K regional panel within 0.3pp.</t>
   </si>
   <si>
     <t>3_Regional</t>
@@ -102,7 +102,7 @@
     <t>Health warning</t>
   </si>
   <si>
-    <t>Like-for-like price is NOT measurable from public data post-reopening. Every external benchmark (CPI lodging, BEA hotels, MAR/HLT RevPAR) has Bonferroni p=1.000 against ABNB ADR ex-FX on 2023Q1+. The unexplained line of +3.97pp in 2025 measures that ignorance; it is not a discovery. Do not build a price forecast on a hotel index.</t>
+    <t>Within-region pricing cannot be separated from SUB-REGIONAL (country) mix, because Airbnb discloses no country-level ADR. The two are carried as one jointly-unidentified term of ~+2.5 to +3.6pp. It is not noise: expansion markets grow ~2x core and are lower-ADR, so it contains a real negative mix component. Separately: every external price benchmark (CPI lodging, BEA hotels, MAR/HLT RevPAR) has Bonferroni p=1.000 against ABNB ADR ex-FX on 2023Q1+, so do NOT build a price forecast on a hotel index.</t>
   </si>
   <si>
     <t>Quarterly ADR history and the ex-FX reconstruction</t>
@@ -237,7 +237,7 @@
     <t>Annual ADR decomposition (pp of ADR y/y)</t>
   </si>
   <si>
-    <t>Price is measured externally, not plugged. The UNEXPLAINED line is the honest residual.</t>
+    <t>REVISED 8 Sep after an audit. The first version carried a large 'unexplained' line that was mostly two method errors: FX was re-derived instead of taken from the letters (wrong by 1.33pp in 2022), and a hotel price proxy with r~0 against ABNB ADR was subtracted as a component. Corrected, the decomposition reconciles to the independent regional panel within 0.3pp.</t>
   </si>
   <si>
     <t>Term</t>
@@ -252,7 +252,7 @@
     <t>What actually printed.</t>
   </si>
   <si>
-    <t>Geographic mix</t>
+    <t>Geographic mix (4-region)</t>
   </si>
   <si>
     <t>Nights shifting to lower-ADR regions. Negative every year and getting worse.</t>
@@ -261,55 +261,61 @@
     <t>FX</t>
   </si>
   <si>
-    <t>Mechanical. Fitted 0.52 - 0.72 x broad USD y/y, r 0.96.</t>
-  </si>
-  <si>
-    <t>Length of stay</t>
+    <t>DISCLOSED in the letters, GBV-weighted - not re-derived. Forecast with 0.52 - 0.72 x broad USD y/y, r 0.96.</t>
+  </si>
+  <si>
+    <t>Interaction</t>
+  </si>
+  <si>
+    <t>Mix x rate cross-term. Small.</t>
+  </si>
+  <si>
+    <t>The residual of the identity. RECONCILES to the independent 10-K regional panel within 0.3pp in 2023-25 - see the check below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   of which length of stay</t>
   </si>
   <si>
     <t>Bounded, not fitted - the panel could not identify an elasticity.</t>
   </si>
   <si>
-    <t>Unit-size mix</t>
+    <t xml:space="preserve">   of which unit-size mix</t>
   </si>
   <si>
     <t>Bedrooms and capacity per booked night, 29 markets. NA/EMEA only.</t>
   </si>
   <si>
-    <t>Like-for-like price (measured)</t>
-  </si>
-  <si>
-    <t>External benchmarks, GBV-weighted. No demonstrated power post-2023.</t>
-  </si>
-  <si>
-    <t>Interaction</t>
-  </si>
-  <si>
-    <t>Mix x rate cross-term. Small.</t>
-  </si>
-  <si>
-    <t>UNEXPLAINED</t>
-  </si>
-  <si>
-    <t>What the decomposition cannot account for. This is a measurement statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  as % of the ADR move</t>
+    <t xml:space="preserve">   of which pricing + SUB-REGIONAL MIX</t>
+  </si>
+  <si>
+    <t>JOINTLY UNIDENTIFIED. Airbnb discloses no country-level ADR, so within-region pricing cannot be separated from country mix. Not noise: expansion markets grow ~2x core and are lower-ADR, so this carries a real negative mix term.</t>
+  </si>
+  <si>
+    <t>Memo: independent regional ex-FX</t>
+  </si>
+  <si>
+    <t>Nights-weighted regional ADR ex-FX built separately from the 10-K.</t>
+  </si>
+  <si>
+    <t>Memo: reconciliation gap</t>
+  </si>
+  <si>
+    <t>Within-region term less the independent build. 2023-25: +0.03, +0.30, -0.13pp.</t>
+  </si>
+  <si>
+    <t>Memo: hotel price comparator</t>
+  </si>
+  <si>
+    <t>COMPARATOR ONLY, never a component. Hotel benchmarks have r~0 with ABNB ADR ex-FX post-2023, so subtracting one would inject variance, not explain it.</t>
   </si>
   <si>
     <t>Confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">not estimable </t>
-  </si>
-  <si>
-    <t>low -- no size</t>
-  </si>
-  <si>
-    <t>low -- size mi</t>
-  </si>
-  <si>
-    <t>medium -- size</t>
+    <t>medium -- reco</t>
+  </si>
+  <si>
+    <t>low -- does no</t>
   </si>
   <si>
     <t>Regional ADR, from the 10-K Geographic Mix tables</t>
@@ -373,6 +379,9 @@
     <t>Take the USD path off the forward curve or a consensus track and apply the fit. This is the only ADR term with demonstrated predictive power. Already in the driver model.</t>
   </si>
   <si>
+    <t>Geographic mix</t>
+  </si>
+  <si>
     <t>Slow, monotonic, and negative every year since 2021: -0.5, -2.8, -1.1, -1.2, -1.6pp. NA nights share fell 39.1% -&gt; 29.6% over five years, roughly 1.5-2pp a year.</t>
   </si>
   <si>
@@ -391,6 +400,9 @@
     <t>Carry ONE number with a band (base ~3.0-3.5%, bear ~2%, bull ~4%) rather than four regional forecasts. Revisit if the spread re-widens - that would be the signal that a region has decoupled.</t>
   </si>
   <si>
+    <t>Unit-size mix</t>
+  </si>
+  <si>
     <t>LOW-MED</t>
   </si>
   <si>
@@ -398,6 +410,9 @@
   </si>
   <si>
     <t>Track it from the quarterly Inside Airbnb capture, and watch whether Airbnb keeps disclosing Bedroom Nights Booked. Treat as a component of the regional pricing number, not a separate forecast line.</t>
+  </si>
+  <si>
+    <t>Length of stay</t>
   </si>
   <si>
     <t>LOW</t>
@@ -1133,7 +1148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="60" customHeight="1">
+    <row r="23" spans="2:3" ht="72" customHeight="1">
       <c r="B23" s="2" t="s">
         <v>26</v>
       </c>
@@ -1867,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
@@ -1880,7 +1895,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="46" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>72</v>
       </c>
@@ -1959,19 +1974,19 @@
         <v>79</v>
       </c>
       <c r="B7" s="8">
-        <v>2.085831915188181</v>
+        <v>2.038661888426363</v>
       </c>
       <c r="C7" s="8">
-        <v>-3.837755192802531</v>
+        <v>-5.167565996429301</v>
       </c>
       <c r="D7" s="8">
-        <v>0.8488690246695254</v>
+        <v>0.1825375170532063</v>
       </c>
       <c r="E7" s="8">
-        <v>-0.2172762084492354</v>
+        <v>-0.4493887530562349</v>
       </c>
       <c r="F7" s="8">
-        <v>1.057150293712707</v>
+        <v>1.304381161007667</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>80</v>
@@ -1982,143 +1997,206 @@
         <v>81</v>
       </c>
       <c r="B8" s="8">
-        <v>0.2691140710941719</v>
+        <v>-0.2176384507396221</v>
       </c>
       <c r="C8" s="8">
-        <v>0.2620573662116254</v>
+        <v>-0.394494037485312</v>
       </c>
       <c r="D8" s="8">
-        <v>0.6174491393177295</v>
+        <v>-0.0494786368971566</v>
       </c>
       <c r="E8" s="8">
-        <v>0.2054051867943019</v>
+        <v>-0.1065834527970392</v>
       </c>
       <c r="F8" s="8">
-        <v>0.0357123713443286</v>
+        <v>-0.1083206075608631</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="9">
+        <f> Within-region ADR ex-FX</f>
+        <v>0</v>
+      </c>
+      <c r="B9" s="10">
+        <v>24.73979171634398</v>
+      </c>
+      <c r="C9" s="10">
+        <v>10.98991180918964</v>
+      </c>
+      <c r="D9" s="10">
+        <v>3.096536844551291</v>
+      </c>
+      <c r="E9" s="10">
+        <v>3.443428221749913</v>
+      </c>
+      <c r="F9" s="10">
+        <v>3.40536100932465</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8">
-        <v>0.4410509947887275</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-0.2513387080576912</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.2691140710941719</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.2620573662116254</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.6174491393177295</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.2054051867943019</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.0357123713443286</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8">
-        <v>6.726</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2.211</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.611</v>
-      </c>
-      <c r="F10" s="8">
-        <v>-0.097</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.4410509947887275</v>
+      </c>
+      <c r="F11" s="8">
+        <v>-0.2513387080576912</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B11" s="8">
-        <v>-0.2176384507396221</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-0.394494037485312</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-0.0494786368971566</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.1065834527970392</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-0.1083206075608631</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="10">
+        <v>24.4706776452498</v>
+      </c>
+      <c r="C12" s="10">
+        <v>10.72785444297801</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2.479087705233562</v>
+      </c>
+      <c r="E12" s="10">
+        <v>2.796972040166883</v>
+      </c>
+      <c r="F12" s="10">
+        <v>3.620987346038013</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10">
-        <v>2.672043639351243</v>
-      </c>
-      <c r="D12" s="10">
-        <v>-0.3982438023827614</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0.9538594955599092</v>
-      </c>
-      <c r="F12" s="10">
-        <v>3.965218213332953</v>
-      </c>
-      <c r="G12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="6"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="6" t="s">
+      <c r="B14" s="8">
+        <v>24.04012221463407</v>
+      </c>
+      <c r="C14" s="8">
+        <v>9.762971585703379</v>
+      </c>
+      <c r="D14" s="8">
+        <v>3.065185946859391</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.145190985222913</v>
+      </c>
+      <c r="F14" s="8">
+        <v>3.536533499367192</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8">
-        <v>99.7168901726687</v>
-      </c>
-      <c r="D13" s="8">
-        <v>18.55080855001432</v>
-      </c>
-      <c r="E13" s="8">
-        <v>58.03539502969186</v>
-      </c>
-      <c r="F13" s="8">
-        <v>131.3984628684031</v>
-      </c>
-      <c r="G13" s="3"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8">
+        <v>0.6996695017099093</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1.226940223486258</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.0313508976919001</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.2982372365269992</v>
+      </c>
+      <c r="F15" s="8">
+        <v>-0.131172490042541</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8">
+        <v>6.726</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2.211</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.611</v>
+      </c>
+      <c r="F16" s="8">
+        <v>-0.097</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="6" t="s">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2" t="s">
         <v>96</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2137,17 +2215,17 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5">
         <v>2020</v>
@@ -2170,7 +2248,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" s="7">
         <v>174.43</v>
@@ -2193,7 +2271,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" s="7">
         <v>98.41</v>
@@ -2216,7 +2294,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="7">
         <v>75.73999999999999</v>
@@ -2239,7 +2317,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B8" s="7">
         <v>85.83</v>
@@ -2262,7 +2340,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="5">
         <v>2020</v>
@@ -2285,7 +2363,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11">
@@ -2306,7 +2384,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11">
@@ -2327,7 +2405,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11">
@@ -2348,7 +2426,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11">
@@ -2369,7 +2447,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="5">
         <v>2020</v>
@@ -2392,7 +2470,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17" s="11">
         <v>39.07867494824017</v>
@@ -2415,7 +2493,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B18" s="11">
         <v>35.04140786749483</v>
@@ -2438,7 +2516,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B19" s="11">
         <v>11.59420289855072</v>
@@ -2461,7 +2539,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B20" s="11">
         <v>14.28571428571429</v>
@@ -2484,7 +2562,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B22" s="5">
         <v>2020</v>
@@ -2507,7 +2585,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10">
@@ -2528,7 +2606,7 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2549,12 +2627,12 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
@@ -2562,13 +2640,13 @@
         <v>73</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="62" customHeight="1">
@@ -2576,83 +2654,83 @@
         <v>79</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="62" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="62" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="62" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="62" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="62" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2672,26 +2750,26 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>35</v>
@@ -2699,7 +2777,7 @@
     </row>
     <row r="5" spans="1:5" ht="26" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B5" s="15">
         <v>3</v>
@@ -2711,12 +2789,12 @@
         <v>-3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="26" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B6" s="15">
         <v>2</v>
@@ -2728,12 +2806,12 @@
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="26" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B7" s="15">
         <v>-2</v>
@@ -2745,12 +2823,12 @@
         <v>-1.2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="26" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B8" s="15">
         <v>-0.15</v>
@@ -2762,12 +2840,12 @@
         <v>-0.05</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="9" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B10" s="16">
         <f>0.52-0.72*B5</f>
@@ -2782,12 +2860,12 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B12" s="16">
         <f>B6+B7+B8</f>
@@ -2802,12 +2880,12 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="9" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B13" s="16">
         <f>B12+B10</f>
@@ -2822,12 +2900,12 @@
         <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B14" s="7">
         <f>183.73*(1+B13/100)</f>
@@ -2842,17 +2920,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2861,7 +2939,7 @@
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2870,7 +2948,7 @@
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2879,7 +2957,7 @@
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2888,7 +2966,7 @@
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>

--- a/model/ADR_decomposition.xlsx
+++ b/model/ADR_decomposition.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="171">
   <si>
     <t>ABNB ADR decomposition</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Scripts</t>
   </si>
   <si>
-    <t>analysis/src/adr/01-10; data in data/processed/adr/. 10 is the audit.</t>
+    <t>analysis/src/adr/01-14; data in data/processed/adr/. 10 is the audit, 11-12 the quote tests, 13 party size, 14a-c length of stay.</t>
   </si>
   <si>
     <t>Rebuild</t>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Mix x rate cross-term. Small.</t>
+  </si>
+  <si>
+    <t>Within Region ADR ex-FX</t>
   </si>
   <si>
     <t>The residual of the identity. RECONCILES to the independent 10-K regional panel within 0.3pp in 2023-25 - see the check below.</t>
@@ -400,28 +403,22 @@
     <t>Carry ONE number with a band (base ~3.0-3.5%, bear ~2%, bull ~4%) rather than four regional forecasts. Revisit if the spread re-widens - that would be the signal that a region has decoupled.</t>
   </si>
   <si>
-    <t>Unit-size mix</t>
-  </si>
-  <si>
-    <t>LOW-MED</t>
-  </si>
-  <si>
-    <t>Small and NA/EMEA-only: +0.63pp of ADR on 29 markets, with APAC +0.08pp and LatAm -0.89pp. Decaying as the mix shift matures.</t>
-  </si>
-  <si>
-    <t>Track it from the quarterly Inside Airbnb capture, and watch whether Airbnb keeps disclosing Bedroom Nights Booked. Treat as a component of the regional pricing number, not a separate forecast line.</t>
-  </si>
-  <si>
-    <t>Length of stay</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>Small in every year (+0.04 to +0.62pp). ALOS drifting down 4.1 -&gt; 3.7 since 2022.</t>
-  </si>
-  <si>
-    <t>Do not forecast separately. The elasticity is not identifiable from disclosed data (fitted value flipped sign across regions and was rejected). Bounded at -0.15.</t>
+    <t>Unit-size mix (party size)</t>
+  </si>
+  <si>
+    <t>Steady and structural: booked capacity per stay +1.2-1.6% a year globally since 2022 (NA +2.5-3%, EMEA +0.5-1%, APAC +1-1.5%, LatAm ~0), worth +0.7-0.9pp of ADR at elasticity 0.59. Does not explain quarter-to-quarter ADR variance (r ~0 vs ex-FX); it is a level term, not a timing signal.</t>
+  </si>
+  <si>
+    <t>13_party_size_adr.py: capacity of the reviewed listing, 123 markets, 15 years, by region. Drive it off the team's people-per-booking forecast at constant fill (d ln capacity = d ln party size), regionally. Bear = mix shift matured (the sleeps-5+ share stalled at 25-27% in 2025-26).</t>
+  </si>
+  <si>
+    <t>Length-of-stay mix</t>
+  </si>
+  <si>
+    <t>Bucket mix term, replaces the rejected elasticity. Per-night price at 7-27 nights is 0.97x and at 28+ is 0.85x an under-7 stay (host + platform discounts, 139 quote dumps, stable across regions). The 28+ share of nights fell 21% (2021) -&gt; ~13-15% (2025-26), about -2pp a year, corroborated by two sources (ALOS identity; calendar runs Sep-25 -&gt; Aug-26). Worth +0.16, +0.33, +0.34, +0.35pp in 2022-25.</t>
+  </si>
+  <si>
+    <t>14a/b/c_los_*.py. Term = sum over buckets of d(nights share) x (price ratio - 1). Base: 28+ share keeps falling ~2pp a year -&gt; +0.3pp. Bear: shares stabilise -&gt; 0. Bull: LatAm-style -3pp -&gt; +0.45pp. The same bucket shares give ALOS for the nights model; do not forecast ALOS separately.</t>
   </si>
   <si>
     <t>Like-for-like price</t>
@@ -461,10 +458,28 @@
     <t>Consensus / forward curve. 3Q26 QTD was -0.4%.</t>
   </si>
   <si>
-    <t>Regional ADR ex-FX, % (converged)</t>
-  </si>
-  <si>
-    <t>2025 nights-weighted was +3.54%; regional spread only 1.5pp.</t>
+    <t>Regional pricing + sub-regional mix, % (ex unit size, ex LOS)</t>
+  </si>
+  <si>
+    <t>2025 within-region ex-FX was +3.5% nights-weighted, of which ~0.7pp was unit-size mix and ~0.35pp length-of-stay mix (rows below). Not measurable externally: a rate with a band, not a forecast.</t>
+  </si>
+  <si>
+    <t>Length-of-stay mix, pp</t>
+  </si>
+  <si>
+    <t>14a/b/c_los_*: 28+ nights share falling ~2pp a year into shorter stays, at per-night ratios 0.97 (7-27n) and 0.85 (28+). Ran +0.16, +0.33, +0.34, +0.35pp in 2022-25. Bear = bucket shares stabilise; bull = LatAm-style -3pp a year.</t>
+  </si>
+  <si>
+    <t>Unit-size mix via party size, pp</t>
+  </si>
+  <si>
+    <t>13_party_size_adr: booked-capacity growth by region (Inside Airbnb reviews, 123 markets, fixed 2019 weights) x price elasticity 0.59, nights-weighted on 10-K 2025 shares. Base = trailing 8-quarter capacity growth; bear = mix shift matured; bull = recent peak. To drive off a people-per-booking forecast: d ln capacity = d ln party size at constant fill.</t>
+  </si>
+  <si>
+    <t>Fee migration reprice, pp</t>
+  </si>
+  <si>
+    <t>ADR is gross of the guest fee, so the single-fee move is +0.7% on the migrated cohort if hosts hold payout, -12.3% if they do not, +3.8% if they over-reprice. Prints reject no-reprice (1H26 NA accelerated). Applies to 4Q26-3Q27 y/y.</t>
   </si>
   <si>
     <t>Geographic mix drag, pp</t>
@@ -485,7 +500,7 @@
     <t>Fitted on 17 disclosed quarters, r 0.96, walk-forward 0.44x naive.</t>
   </si>
   <si>
-    <t>ADR ex-FX y/y, %  = regional pricing + mix + interaction</t>
+    <t>ADR ex-FX y/y, %  = pricing + LOS mix + unit size + fee + geo mix + interaction</t>
   </si>
   <si>
     <t>This is what the letters would report as ex-FX ADR. Note it is 1.5-1.8pp BELOW the regional pricing number - that gap is geographic mix.</t>
@@ -2016,9 +2031,8 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="9">
-        <f> Within-region ADR ex-FX</f>
-        <v>0</v>
+      <c r="A9" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="B9" s="10">
         <v>24.73979171634398</v>
@@ -2036,12 +2050,12 @@
         <v>3.40536100932465</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" s="8">
         <v>0.2691140710941719</v>
@@ -2059,12 +2073,12 @@
         <v>0.0357123713443286</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
@@ -2082,12 +2096,12 @@
         <v>-0.2513387080576912</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" s="10">
         <v>24.4706776452498</v>
@@ -2105,7 +2119,7 @@
         <v>3.620987346038013</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2114,7 +2128,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8">
         <v>24.04012221463407</v>
@@ -2132,12 +2146,12 @@
         <v>3.536533499367192</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="8">
         <v>0.6996695017099093</v>
@@ -2155,12 +2169,12 @@
         <v>-0.131172490042541</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8">
@@ -2176,27 +2190,27 @@
         <v>-0.097</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="E18" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2215,17 +2229,17 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5">
         <v>2020</v>
@@ -2248,7 +2262,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="7">
         <v>174.43</v>
@@ -2271,7 +2285,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="7">
         <v>98.41</v>
@@ -2294,7 +2308,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" s="7">
         <v>75.73999999999999</v>
@@ -2317,7 +2331,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="7">
         <v>85.83</v>
@@ -2340,7 +2354,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="5">
         <v>2020</v>
@@ -2363,7 +2377,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11">
@@ -2384,7 +2398,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11">
@@ -2405,7 +2419,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11">
@@ -2426,7 +2440,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11">
@@ -2447,7 +2461,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="5">
         <v>2020</v>
@@ -2470,7 +2484,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17" s="11">
         <v>39.07867494824017</v>
@@ -2493,7 +2507,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B18" s="11">
         <v>35.04140786749483</v>
@@ -2516,7 +2530,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="11">
         <v>11.59420289855072</v>
@@ -2539,7 +2553,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20" s="11">
         <v>14.28571428571429</v>
@@ -2562,7 +2576,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B22" s="5">
         <v>2020</v>
@@ -2585,7 +2599,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10">
@@ -2606,7 +2620,7 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2627,12 +2641,12 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
@@ -2640,13 +2654,13 @@
         <v>73</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="62" customHeight="1">
@@ -2654,49 +2668,49 @@
         <v>79</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="62" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="62" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="62" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>128</v>
@@ -2709,28 +2723,28 @@
       <c r="A9" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="62" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2740,7 +2754,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -2750,34 +2764,34 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="26" customHeight="1">
+    <row r="5" spans="1:5" ht="40" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B5" s="15">
         <v>3</v>
@@ -2789,175 +2803,199 @@
         <v>-3</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="40" customHeight="1">
+      <c r="A6" s="6" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="26" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="C6" s="15">
+        <v>2.2</v>
+      </c>
+      <c r="D6" s="15">
+        <v>2.55</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="15">
-        <v>2</v>
-      </c>
-      <c r="C6" s="15">
-        <v>3.25</v>
-      </c>
-      <c r="D6" s="15">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="40" customHeight="1">
+      <c r="A7" s="6" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="26" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="15">
+        <v>0</v>
+      </c>
+      <c r="C7" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0.45</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="15">
+    </row>
+    <row r="8" spans="1:5" ht="40" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0.74</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.98</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="40" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="15">
+        <v>-0.5</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="40" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="15">
         <v>-2</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C10" s="15">
         <v>-1.7</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D10" s="15">
         <v>-1.2</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="26" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="E10" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="40" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="15">
         <v>-0.15</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C11" s="15">
         <v>-0.1</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D11" s="15">
         <v>-0.05</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B10" s="16">
+      <c r="E11" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="16">
         <f>0.52-0.72*B5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C13" s="16">
         <f>0.52-0.72*C5</f>
         <v>0</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D13" s="16">
         <f>0.52-0.72*D5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" customHeight="1">
-      <c r="A12" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="16">
-        <f>B6+B7+B8</f>
+      <c r="E13" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="16">
+        <f>B6+B7+B8+B9+B10+B11</f>
         <v>0</v>
       </c>
-      <c r="C12" s="16">
-        <f>C6+C7+C8</f>
+      <c r="C15" s="16">
+        <f>C6+C7+C8+C9+C10+C11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="16">
-        <f>D6+D7+D8</f>
+      <c r="D15" s="16">
+        <f>D6+D7+D8+D9+D10+D11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="B13" s="16">
-        <f>B12+B10</f>
+      <c r="E15" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="16">
+        <f>B15+B13</f>
         <v>0</v>
       </c>
-      <c r="C13" s="16">
-        <f>C12+C10</f>
+      <c r="C16" s="16">
+        <f>C15+C13</f>
         <v>0</v>
       </c>
-      <c r="D13" s="16">
-        <f>D12+D10</f>
+      <c r="D16" s="16">
+        <f>D15+D13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="7">
-        <f>183.73*(1+B13/100)</f>
+      <c r="E16" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="7">
+        <f>183.73*(1+B16/100)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="7">
-        <f>183.73*(1+C13/100)</f>
+      <c r="C17" s="7">
+        <f>183.73*(1+C16/100)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="7">
-        <f>183.73*(1+D13/100)</f>
+      <c r="D17" s="7">
+        <f>183.73*(1+D16/100)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2966,20 +3004,47 @@
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
+    <row r="23" spans="1:5" ht="30" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" ht="30" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" ht="30" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/model/ADR_decomposition.xlsx
+++ b/model/ADR_decomposition.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="176">
   <si>
     <t>ABNB ADR decomposition</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Scripts</t>
   </si>
   <si>
-    <t>analysis/src/adr/01-14; data in data/processed/adr/. 10 is the audit, 11-12 the quote tests, 13 party size, 14a-c length of stay.</t>
+    <t>analysis/src/adr/01-15; data in data/processed/adr/. 10 is the audit, 11-12 the quote tests, 13 party size, 14a-c length of stay, 15 seats dilution.</t>
   </si>
   <si>
     <t>Rebuild</t>
@@ -421,6 +421,15 @@
     <t>14a/b/c_los_*.py. Term = sum over buckets of d(nights share) x (price ratio - 1). Base: 28+ share keeps falling ~2pp a year -&gt; +0.3pp. Bear: shares stabilise -&gt; 0. Bull: LatAm-style -3pp -&gt; +0.45pp. The same bucket shares give ALOS for the nights model; do not forecast ALOS separately.</t>
   </si>
   <si>
+    <t>New-business mix (seats + hotels)</t>
+  </si>
+  <si>
+    <t>Denominator effect: ADR = GBV / Nights AND Seats. Experiences seats (~0.43x a home night), Services seats (~0.69x) and hotel nights (~0.81x) dilute reported ADR as their share rises. FY25 ~-0.18pp (mostly hotels); base FY26 -0.48, FY27 -0.57pp; business-bull FY27 -1.05pp. Regional ADR is on the same basis, so it hits the regional figures too.</t>
+  </si>
+  <si>
+    <t>15_seats_dilution.py, driven by 11_new_business_scenarios. Volumes are undisclosed; the soft input is GBV per seat ($75 experiences, $120 services; FY27 base drag -0.3 to -1.0pp across the grid). Tie the case to the revenue build's new-business case so ADR and revenue move together. A reader who sees ADR decelerate and calls it pricing weakness is wrong if this is the cause.</t>
+  </si>
+  <si>
     <t>Like-for-like price</t>
   </si>
   <si>
@@ -488,6 +497,12 @@
     <t>Ran -1.1, -1.2, -1.6pp in 2023-25. Drive off the regional nights build.</t>
   </si>
   <si>
+    <t>New-business mix (seats + hotels), pp</t>
+  </si>
+  <si>
+    <t>15_seats_dilution: ADR = GBV / Nights AND Seats, so Experiences and Services seats (~0.43x and ~0.69x a home night) and hotel nights (~0.81x) dilute reported ADR as their share of the denominator rises. Scenario build off 11_new_business_scenarios (volumes are not disclosed): FY25 -0.18pp, FY27 base -0.57pp. Bear ADR = bull business case. Ticket per seat is the soft assumption ($75 / $120).</t>
+  </si>
+  <si>
     <t>Interaction, pp</t>
   </si>
   <si>
@@ -500,7 +515,7 @@
     <t>Fitted on 17 disclosed quarters, r 0.96, walk-forward 0.44x naive.</t>
   </si>
   <si>
-    <t>ADR ex-FX y/y, %  = pricing + LOS mix + unit size + fee + geo mix + interaction</t>
+    <t>ADR ex-FX y/y, %  = pricing + LOS mix + unit size + fee + geo mix + new-business mix + interaction</t>
   </si>
   <si>
     <t>This is what the letters would report as ex-FX ADR. Note it is 1.5-1.8pp BELOW the regional pricing number - that gap is geographic mix.</t>
@@ -2630,7 +2645,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2737,14 +2752,28 @@
       <c r="A10" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="62" customHeight="1">
+      <c r="A11" s="9" t="s">
         <v>136</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2754,7 +2783,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -2764,26 +2793,26 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>35</v>
@@ -2791,7 +2820,7 @@
     </row>
     <row r="5" spans="1:5" ht="40" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B5" s="15">
         <v>3</v>
@@ -2803,12 +2832,12 @@
         <v>-3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="40" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B6" s="15">
         <v>1.5</v>
@@ -2820,12 +2849,12 @@
         <v>2.55</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="40" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B7" s="15">
         <v>0</v>
@@ -2837,12 +2866,12 @@
         <v>0.45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="40" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B8" s="15">
         <v>0</v>
@@ -2854,12 +2883,12 @@
         <v>0.98</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="40" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B9" s="15">
         <v>-0.5</v>
@@ -2871,12 +2900,12 @@
         <v>1.5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="40" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B10" s="15">
         <v>-2</v>
@@ -2888,123 +2917,131 @@
         <v>-1.2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="40" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B11" s="15">
+        <v>-1.05</v>
+      </c>
+      <c r="C11" s="15">
+        <v>-0.57</v>
+      </c>
+      <c r="D11" s="15">
+        <v>-0.2</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="40" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="15">
         <v>-0.15</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C12" s="15">
         <v>-0.1</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D12" s="15">
         <v>-0.05</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" s="16">
+      <c r="E12" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="16">
         <f>0.52-0.72*B5</f>
         <v>0</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C14" s="16">
         <f>0.52-0.72*C5</f>
         <v>0</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D14" s="16">
         <f>0.52-0.72*D5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="16">
-        <f>B6+B7+B8+B9+B10+B11</f>
+      <c r="E14" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="16">
+        <f>B6+B7+B8+B9+B10+B11+B12</f>
         <v>0</v>
       </c>
-      <c r="C15" s="16">
-        <f>C6+C7+C8+C9+C10+C11</f>
+      <c r="C16" s="16">
+        <f>C6+C7+C8+C9+C10+C11+C12</f>
         <v>0</v>
       </c>
-      <c r="D15" s="16">
-        <f>D6+D7+D8+D9+D10+D11</f>
+      <c r="D16" s="16">
+        <f>D6+D7+D8+D9+D10+D11+D12</f>
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="16">
-        <f>B15+B13</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="16">
-        <f>C15+C13</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="16">
-        <f>D15+D13</f>
-        <v>0</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="7">
-        <f>183.73*(1+B16/100)</f>
+        <v>166</v>
+      </c>
+      <c r="B17" s="16">
+        <f>B16+B14</f>
         <v>0</v>
       </c>
-      <c r="C17" s="7">
-        <f>183.73*(1+C16/100)</f>
+      <c r="C17" s="16">
+        <f>C16+C14</f>
         <v>0</v>
       </c>
-      <c r="D17" s="7">
-        <f>183.73*(1+D16/100)</f>
+      <c r="D17" s="16">
+        <f>D16+D14</f>
         <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="7">
+        <f>183.73*(1+B17/100)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="7">
+        <f>183.73*(1+C17/100)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <f>183.73*(1+D17/100)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -3013,7 +3050,7 @@
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -3022,7 +3059,7 @@
     </row>
     <row r="24" spans="1:5" ht="30" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -3031,20 +3068,29 @@
     </row>
     <row r="25" spans="1:5" ht="30" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
+    <row r="26" spans="1:5" ht="30" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
